--- a/ig/DM-37/CodeSystem-TRE-R244-CategorieOrganisation.xlsx
+++ b/ig/DM-37/CodeSystem-TRE-R244-CategorieOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="317">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-26T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -403,7 +403,10 @@
     <t>40</t>
   </si>
   <si>
-    <t>Maison d'accueil spécialisé (MAS)</t>
+    <t>Maison d'accueil spécialisée (MAS)</t>
+  </si>
+  <si>
+    <t>Structure d'hébergement permanent et de soins pour adulte handicapé dépendant qui n'arrive pas à réaliser seul les actes de la vie courante (se nourrir, s'habiller...), elles proposent des activités quotidiennes d'éveil ou occupationnelles (musique, relaxation, activités manuelles…) et sont structurées autour d'unités de vie comprenant 8 à 10 chambres individuelles. Elles accueillent des personnes un peu plus dépendantes que la population hébergée en foyer d'accueil médicalisé (Fam)</t>
   </si>
   <si>
     <t>41</t>
@@ -499,7 +502,7 @@
     <t>56</t>
   </si>
   <si>
-    <t>Unité d'enseignement externe</t>
+    <t>Unité d'enseignement externalisée</t>
   </si>
   <si>
     <t>57</t>
@@ -908,6 +911,60 @@
   </si>
   <si>
     <t>Unité de soins intensifs (USI) de spécialité</t>
+  </si>
+  <si>
+    <t>125</t>
+  </si>
+  <si>
+    <t>Centre de protection maternelle et infantile (PMI)</t>
+  </si>
+  <si>
+    <t>126</t>
+  </si>
+  <si>
+    <t>Structure Douleur Chronique (SDC)</t>
+  </si>
+  <si>
+    <t>127</t>
+  </si>
+  <si>
+    <t>Centre régional du psychotraumatisme (CRP)</t>
+  </si>
+  <si>
+    <t>128</t>
+  </si>
+  <si>
+    <t>Unité d'hospitalisation à domicile socle</t>
+  </si>
+  <si>
+    <t>129</t>
+  </si>
+  <si>
+    <t>Unité d'hospitalisation à domicile ante et post-partum</t>
+  </si>
+  <si>
+    <t>130</t>
+  </si>
+  <si>
+    <t>Unité d'hospitalisation à domicile réadaptation</t>
+  </si>
+  <si>
+    <t>131</t>
+  </si>
+  <si>
+    <t>Unité d'hospitalisation à domicile enfants de moins de trois ans</t>
+  </si>
+  <si>
+    <t>132</t>
+  </si>
+  <si>
+    <t>Service autonomie à domicile (SAD) aide et soins</t>
+  </si>
+  <si>
+    <t>133</t>
+  </si>
+  <si>
+    <t>Service autonomie à domicile (SAD) aide</t>
   </si>
 </sst>
 </file>
@@ -1281,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D125"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1776,17 +1833,19 @@
       <c r="C41" t="s" s="2">
         <v>129</v>
       </c>
-      <c r="D41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>130</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
         <v>49</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C42" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D42" s="2"/>
     </row>
@@ -1795,10 +1854,10 @@
         <v>49</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D43" s="2"/>
     </row>
@@ -1807,10 +1866,10 @@
         <v>49</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D44" s="2"/>
     </row>
@@ -1819,10 +1878,10 @@
         <v>49</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D45" s="2"/>
     </row>
@@ -1831,10 +1890,10 @@
         <v>49</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C46" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D46" s="2"/>
     </row>
@@ -1843,10 +1902,10 @@
         <v>49</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="D47" s="2"/>
     </row>
@@ -1855,10 +1914,10 @@
         <v>49</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D48" s="2"/>
     </row>
@@ -1867,10 +1926,10 @@
         <v>49</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D49" s="2"/>
     </row>
@@ -1879,10 +1938,10 @@
         <v>49</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D50" s="2"/>
     </row>
@@ -1891,10 +1950,10 @@
         <v>49</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D51" s="2"/>
     </row>
@@ -1903,10 +1962,10 @@
         <v>49</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D52" s="2"/>
     </row>
@@ -1915,10 +1974,10 @@
         <v>49</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D53" s="2"/>
     </row>
@@ -1927,10 +1986,10 @@
         <v>49</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D54" s="2"/>
     </row>
@@ -1939,10 +1998,10 @@
         <v>49</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D55" s="2"/>
     </row>
@@ -1951,10 +2010,10 @@
         <v>49</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D56" s="2"/>
     </row>
@@ -1963,10 +2022,10 @@
         <v>49</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D57" s="2"/>
     </row>
@@ -1975,10 +2034,10 @@
         <v>49</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D58" s="2"/>
     </row>
@@ -1987,10 +2046,10 @@
         <v>49</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D59" s="2"/>
     </row>
@@ -1999,10 +2058,10 @@
         <v>49</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D60" s="2"/>
     </row>
@@ -2011,10 +2070,10 @@
         <v>49</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D61" s="2"/>
     </row>
@@ -2023,10 +2082,10 @@
         <v>49</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D62" s="2"/>
     </row>
@@ -2035,10 +2094,10 @@
         <v>49</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D63" s="2"/>
     </row>
@@ -2047,10 +2106,10 @@
         <v>49</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D64" s="2"/>
     </row>
@@ -2059,10 +2118,10 @@
         <v>49</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D65" s="2"/>
     </row>
@@ -2071,10 +2130,10 @@
         <v>49</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D66" s="2"/>
     </row>
@@ -2083,10 +2142,10 @@
         <v>49</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D67" s="2"/>
     </row>
@@ -2095,10 +2154,10 @@
         <v>49</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D68" s="2"/>
     </row>
@@ -2107,10 +2166,10 @@
         <v>49</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D69" s="2"/>
     </row>
@@ -2119,10 +2178,10 @@
         <v>49</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D70" s="2"/>
     </row>
@@ -2131,10 +2190,10 @@
         <v>49</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="D71" s="2"/>
     </row>
@@ -2143,10 +2202,10 @@
         <v>49</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D72" s="2"/>
     </row>
@@ -2155,10 +2214,10 @@
         <v>49</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D73" s="2"/>
     </row>
@@ -2167,10 +2226,10 @@
         <v>49</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="D74" s="2"/>
     </row>
@@ -2179,10 +2238,10 @@
         <v>49</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D75" s="2"/>
     </row>
@@ -2191,10 +2250,10 @@
         <v>49</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="D76" s="2"/>
     </row>
@@ -2203,10 +2262,10 @@
         <v>49</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D77" s="2"/>
     </row>
@@ -2215,10 +2274,10 @@
         <v>49</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D78" s="2"/>
     </row>
@@ -2227,10 +2286,10 @@
         <v>49</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D79" s="2"/>
     </row>
@@ -2239,10 +2298,10 @@
         <v>49</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C80" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="D80" s="2"/>
     </row>
@@ -2251,10 +2310,10 @@
         <v>49</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C81" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D81" s="2"/>
     </row>
@@ -2263,10 +2322,10 @@
         <v>49</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C82" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D82" s="2"/>
     </row>
@@ -2275,10 +2334,10 @@
         <v>49</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C83" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D83" s="2"/>
     </row>
@@ -2287,10 +2346,10 @@
         <v>49</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D84" s="2"/>
     </row>
@@ -2299,10 +2358,10 @@
         <v>49</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D85" s="2"/>
     </row>
@@ -2311,10 +2370,10 @@
         <v>49</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="D86" s="2"/>
     </row>
@@ -2323,10 +2382,10 @@
         <v>49</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D87" s="2"/>
     </row>
@@ -2335,10 +2394,10 @@
         <v>49</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D88" s="2"/>
     </row>
@@ -2347,10 +2406,10 @@
         <v>49</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="D89" s="2"/>
     </row>
@@ -2359,10 +2418,10 @@
         <v>49</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D90" s="2"/>
     </row>
@@ -2371,10 +2430,10 @@
         <v>49</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D91" s="2"/>
     </row>
@@ -2383,10 +2442,10 @@
         <v>49</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C92" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D92" s="2"/>
     </row>
@@ -2395,10 +2454,10 @@
         <v>49</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C93" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D93" s="2"/>
     </row>
@@ -2407,10 +2466,10 @@
         <v>49</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C94" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D94" s="2"/>
     </row>
@@ -2419,10 +2478,10 @@
         <v>49</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="D95" s="2"/>
     </row>
@@ -2431,10 +2490,10 @@
         <v>49</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C96" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D96" s="2"/>
     </row>
@@ -2443,10 +2502,10 @@
         <v>49</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D97" s="2"/>
     </row>
@@ -2455,10 +2514,10 @@
         <v>49</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D98" s="2"/>
     </row>
@@ -2467,10 +2526,10 @@
         <v>49</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D99" s="2"/>
     </row>
@@ -2479,10 +2538,10 @@
         <v>49</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D100" s="2"/>
     </row>
@@ -2491,10 +2550,10 @@
         <v>49</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D101" s="2"/>
     </row>
@@ -2503,10 +2562,10 @@
         <v>49</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D102" s="2"/>
     </row>
@@ -2515,10 +2574,10 @@
         <v>49</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="D103" s="2"/>
     </row>
@@ -2527,10 +2586,10 @@
         <v>49</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="D104" s="2"/>
     </row>
@@ -2539,10 +2598,10 @@
         <v>49</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="D105" s="2"/>
     </row>
@@ -2551,10 +2610,10 @@
         <v>49</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D106" s="2"/>
     </row>
@@ -2563,10 +2622,10 @@
         <v>49</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D107" s="2"/>
     </row>
@@ -2575,10 +2634,10 @@
         <v>49</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="D108" s="2"/>
     </row>
@@ -2587,10 +2646,10 @@
         <v>49</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="D109" s="2"/>
     </row>
@@ -2599,10 +2658,10 @@
         <v>49</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D110" s="2"/>
     </row>
@@ -2611,10 +2670,10 @@
         <v>49</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D111" s="2"/>
     </row>
@@ -2623,10 +2682,10 @@
         <v>49</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D112" s="2"/>
     </row>
@@ -2635,10 +2694,10 @@
         <v>49</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D113" s="2"/>
     </row>
@@ -2647,10 +2706,10 @@
         <v>49</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D114" s="2"/>
     </row>
@@ -2659,10 +2718,10 @@
         <v>49</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D115" s="2"/>
     </row>
@@ -2671,10 +2730,10 @@
         <v>49</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D116" s="2"/>
     </row>
@@ -2683,10 +2742,10 @@
         <v>49</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="D117" s="2"/>
     </row>
@@ -2695,10 +2754,10 @@
         <v>49</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D118" s="2"/>
     </row>
@@ -2707,10 +2766,10 @@
         <v>49</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="D119" s="2"/>
     </row>
@@ -2719,10 +2778,10 @@
         <v>49</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D120" s="2"/>
     </row>
@@ -2731,10 +2790,10 @@
         <v>49</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="D121" s="2"/>
     </row>
@@ -2743,10 +2802,10 @@
         <v>49</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="D122" s="2"/>
     </row>
@@ -2755,10 +2814,10 @@
         <v>49</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D123" s="2"/>
     </row>
@@ -2767,10 +2826,10 @@
         <v>49</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D124" s="2"/>
     </row>
@@ -2779,12 +2838,120 @@
         <v>49</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="D125" s="2"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B126" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="D126" s="2"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B127" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="C127" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="D127" s="2"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="C128" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="D128" s="2"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="C129" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="D129" s="2"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="C130" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="D130" s="2"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="C131" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="D131" s="2"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="C132" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="D132" s="2"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B133" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="C133" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="D133" s="2"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B134" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="C134" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="D134" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
